--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/RETENTOR PARTIDA.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/RETENTOR PARTIDA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,7 +449,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>RETENTOR PART IRON TITAN FAN CG125-150/ BIZ125/ BROS NXR125-150 041633</t>
+          <t>RETENTOR PARTIDA IRON TITAN FAN CG125-150/ BIZ125/ BROS NXR125-150 041633</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -470,7 +470,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>RETENTOR PART IRON YBR125/ XTZ125 176232</t>
+          <t>RETENTOR PARTIDA IRON YBR125/ XTZ125 176232</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -491,7 +491,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>RETENTOR PART IRON FAN125/ TITAN150/ NXR BROS150 2006 A 2016/ BIZ125 185509</t>
+          <t>RETENTOR PARTIDA IRON FAN125/ TITAN150/ NXR BROS150 2006 A 2016/ BIZ125 185509</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -507,17 +507,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7895099124439</t>
+          <t xml:space="preserve"> 7899468086335</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RETENTOR PINHA IRON CG FAN TITAN 2000 KS/ TITAN150 041646</t>
+          <t>RETENTOR PARTIDA TRILHA CG TITAN FAN 150/ FAN125/ BIZ125/ BROS NXR150</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -528,17 +528,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 7899468086335</t>
+          <t>7908305613549</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RETENTOR PART TRILHA CG TITAN FAN 150/ FAN125/ BIZ125/ BROS NXR150</t>
+          <t>RETENTOR PARTIDA TRILHA YBR125 2000 A 2008/ FACTOR125 2009 A 2016/ XTZ125 2003 A 2016</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -549,17 +549,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7908305613549</t>
+          <t>7899641801144</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RETENTOR PART TRILHA YBR125 2000 A 2008/ FACTOR125 2009 A 2016/ XTZ125 2003 A 2016</t>
+          <t xml:space="preserve"> RETENTOR PARTIDA VEDAMOTORS CG FAN125-150/ BIZ125/ MAX FIRE150</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -570,17 +570,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7899641801144</t>
+          <t>7899641801175</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> RETENTOR PART VEDAMOTORS CG FAN125-150/ BIZ125/ MAX FIRE150</t>
+          <t>RETENTOR PARTIDA VEDAMOTORS BIZ 100/ POP100/ JET/ SHR</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -591,17 +591,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7899641801175</t>
+          <t>7899641801120</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>RETENTOR PART VEDAMOTORS BIZ 100/ POP100/ JET/ SHR</t>
+          <t>RETENTOR PARTIDA VEDAMOTORS CBX250/ NEXT/ BROS NXRO125-150/ CBX200/ CRF230</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -612,17 +612,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7899641801120</t>
+          <t>7909201088974</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>RETENTOR PART VEDAMOTORS CBX250/ NEXT/ BROS NXRO125-150/ CBX200/ CRF230</t>
+          <t>RETENTOR PARTIDA MOTOPORT CG 1995 A 2008/ TITAN CG150 2004 A 2015</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -633,41 +633,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7909201088974</t>
+          <t>7898733220016</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>RETENTOR PART MOTOPORT CG 1995 A 2008/ TITAN CG150 2004 A 2015</t>
+          <t>RETENTOR PARTIDA BHD SUSUKI YES125</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>7898733220016</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>RETENTOR PART BHD SUSUKI YES125</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/RETENTOR PARTIDA.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/RETENTOR PARTIDA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -449,7 +444,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>RETENTOR PARTIDA IRON TITAN FAN CG125-150/ BIZ125/ BROS NXR125-150 041633</t>
+          <t>RETENTOR PEDAL PARTIDA IRON TITAN FAN CG125-150/ BIZ125/ BROS NXR125-150 041633</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -457,7 +452,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -470,7 +464,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>RETENTOR PARTIDA IRON YBR125/ XTZ125 176232</t>
+          <t>RETENTOR PEDAL PARTIDA IRON YBR125/ XTZ125 176232</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -478,7 +472,6 @@
           <t>18</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -491,7 +484,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>RETENTOR PARTIDA IRON FAN125/ TITAN150/ NXR BROS150 2006 A 2016/ BIZ125 185509</t>
+          <t>RETENTOR PEDAL PARTIDA IRON FAN125/ TITAN150/ NXR BROS150 2006 A 2016/ BIZ125 185509</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -499,7 +492,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -512,7 +504,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RETENTOR PARTIDA TRILHA CG TITAN FAN 150/ FAN125/ BIZ125/ BROS NXR150</t>
+          <t>RETENTOR PEDAL PARTIDA TRILHA CG TITAN FAN 150/ FAN125/ BIZ125/ BROS NXR150</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -520,7 +512,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -533,7 +524,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RETENTOR PARTIDA TRILHA YBR125 2000 A 2008/ FACTOR125 2009 A 2016/ XTZ125 2003 A 2016</t>
+          <t>RETENTOR PEDAL PARTIDA TRILHA YBR125 2000 A 2008/ FACTOR125 2009 A 2016/ XTZ125 2003 A 2016</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -541,7 +532,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -554,7 +544,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> RETENTOR PARTIDA VEDAMOTORS CG FAN125-150/ BIZ125/ MAX FIRE150</t>
+          <t xml:space="preserve"> RETENTOR PEDAL PARTIDA VEDAMOTORS CG FAN125-150/ BIZ125/ MAX FIRE150</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -562,7 +552,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -575,7 +564,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RETENTOR PARTIDA VEDAMOTORS BIZ 100/ POP100/ JET/ SHR</t>
+          <t>RETENTOR PEDAL PARTIDA VEDAMOTORS BIZ 100/ POP100/ JET/ SHR</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -583,7 +572,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -596,7 +584,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>RETENTOR PARTIDA VEDAMOTORS CBX250/ NEXT/ BROS NXRO125-150/ CBX200/ CRF230</t>
+          <t>RETENTOR PEDAL PARTIDA VEDAMOTORS CBX250/ NEXT/ BROS NXRO125-150/ CBX200/ CRF230</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -604,7 +592,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -617,7 +604,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>RETENTOR PARTIDA MOTOPORT CG 1995 A 2008/ TITAN CG150 2004 A 2015</t>
+          <t>RETENTOR PEDAL PARTIDA MOTOPORT CG 1995 A 2008/ TITAN CG150 2004 A 2015</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -625,7 +612,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -638,7 +624,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>RETENTOR PARTIDA BHD SUSUKI YES125</t>
+          <t>RETENTOR PEDAL PARTIDA BHD SUSUKI YES125</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -646,7 +632,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
